--- a/estimate_forms/033_request_a_free_estimate--estimate_forms.xlsx
+++ b/estimate_forms/033_request_a_free_estimate--estimate_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -832,12 +832,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'general_construction'}</t>
+          <t>general_construction</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'General Construction'}</t>
+          <t>General Construction</t>
         </is>
       </c>
     </row>
@@ -849,12 +849,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'home_improvement'}</t>
+          <t>home_improvement</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Home Improvement'}</t>
+          <t>Home Improvement</t>
         </is>
       </c>
     </row>
@@ -866,12 +866,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -883,12 +883,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'general_labor'}</t>
+          <t>general_labor</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'General Labor'}</t>
+          <t>General Labor</t>
         </is>
       </c>
     </row>
@@ -900,12 +900,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'labor_+_materials'}</t>
+          <t>labor_+_materials</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Labor + Materials'}</t>
+          <t>Labor + Materials</t>
         </is>
       </c>
     </row>
@@ -917,12 +917,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'service_only'}</t>
+          <t>service_only</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Service Only'}</t>
+          <t>Service Only</t>
         </is>
       </c>
     </row>
@@ -934,12 +934,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'upload_documents'}</t>
+          <t>upload_documents</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Upload Documents'}</t>
+          <t>Upload Documents</t>
         </is>
       </c>
     </row>
@@ -951,12 +951,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'share_location'}</t>
+          <t>share_location</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Share Location'}</t>
+          <t>Share Location</t>
         </is>
       </c>
     </row>
@@ -968,12 +968,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'other_(optional)'}</t>
+          <t>other_(optional)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Other (optional)'}</t>
+          <t>Other (optional)</t>
         </is>
       </c>
     </row>
@@ -985,12 +985,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'i_confirm_i_have_read_the_estimate_request_form.'}</t>
+          <t>i_confirm_i_have_read_the_estimate_request_form.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'I confirm I have read the estimate request form.'}</t>
+          <t>I confirm I have read the estimate request form.</t>
         </is>
       </c>
     </row>
@@ -1002,12 +1002,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'i_do_not_confirm_i_have_read_the_estimate_request_form.'}</t>
+          <t>i_do_not_confirm_i_have_read_the_estimate_request_form.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'I do not confirm I have read the estimate request form.'}</t>
+          <t>I do not confirm I have read the estimate request form.</t>
         </is>
       </c>
     </row>
